--- a/excel_templates/wgs_wxs_panel_manifest_template.xlsx
+++ b/excel_templates/wgs_wxs_panel_manifest_template.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Lists" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Data Dictionary'!$A$1:$G$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Data Dictionary'!$A$1:$G$50</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G48"/>
+  <dimension ref="A1:G50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1647,7 +1647,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>total_reads</t>
+          <t>is_adapter_trimmed</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -1657,18 +1657,22 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Total number of reads that align to the reference.</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr"/>
+          <t>Were adapters trimmed from sequencing data? Not required, as adapter presence is detected downstream; fill in if known. Only applies to FASTQ files.</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>"True", "False", "Unknown"</t>
+        </is>
+      </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>boolean/string</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>525600</t>
+          <t>True</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr"/>
@@ -1676,7 +1680,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>mean_coverage</t>
+          <t>adapter_sequencing</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -1686,18 +1690,18 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Mean coverage for whole genome sequencing, or mean target coverage for whole exome and targeted sequencing, collected from Picard Tools.</t>
+          <t>Base sequence of the sequencing adapter. Only applies when adapters were not trimmed.</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr"/>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>GCAT</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr"/>
@@ -1705,28 +1709,28 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>reference_genome</t>
+          <t>total_reads</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Reference genome version.</t>
+          <t>Total number of reads that align to the reference.</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr"/>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>GRCH38</t>
+          <t>525600</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr"/>
@@ -1734,32 +1738,28 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>FFPE</t>
+          <t>mean_coverage</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Is the sample preserved in FFPE</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>"True", "False"</t>
-        </is>
-      </c>
+          <t>Mean coverage for whole genome sequencing, or mean target coverage for whole exome and targeted sequencing, collected from Picard Tools.</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr"/>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>60</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr"/>
@@ -1767,7 +1767,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>PI_name</t>
+          <t>reference_genome</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -1777,7 +1777,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Principal Investigator of the project</t>
+          <t>Reference genome version.</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr"/>
@@ -1788,19 +1788,15 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Fonseca</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
+          <t>GRCH38</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>project</t>
+          <t>FFPE</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -1810,30 +1806,30 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Short name of the project</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr"/>
+          <t>Is the sample preserved in FFPE</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>"True", "False"</t>
+        </is>
+      </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>impact trial</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>organism</t>
+          <t>PI_name</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -1843,14 +1839,10 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Binomial name of organism with full genus name</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>"Homo sapiens", "Mus musculus"</t>
-        </is>
-      </c>
+          <t>Principal Investigator of the project</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr"/>
       <c r="E47" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -1858,50 +1850,120 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Homo sapiens</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr"/>
+          <t>Fonseca</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>project</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Short name of the project</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr"/>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>impact trial</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>organism</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Binomial name of organism with full genus name</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>"Homo sapiens", "Mus musculus"</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>Homo sapiens</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
           <t>host_organism</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
         <is>
           <t>Host organism binomial name when the sequenced sample is a xenograft. Required when compisition is "Patient Derived Xenograft" or "Xenograft"</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>"Mus musculus"</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Mus musculus</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G48"/>
+  <autoFilter ref="A1:G50"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/excel_templates/wgs_wxs_panel_manifest_template.xlsx
+++ b/excel_templates/wgs_wxs_panel_manifest_template.xlsx
@@ -1974,7 +1974,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU1"/>
+  <dimension ref="A1:AW1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2024,6 +2024,8 @@
     <col width="24" customWidth="1" min="45" max="45"/>
     <col width="24" customWidth="1" min="46" max="46"/>
     <col width="24" customWidth="1" min="47" max="47"/>
+    <col width="24" customWidth="1" min="48" max="48"/>
+    <col width="24" customWidth="1" min="49" max="49"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2224,47 +2226,57 @@
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
+          <t>is_adapter_trimmed</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>adapter_sequencing</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
           <t>total_reads</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>mean_coverage</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>reference_genome</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>FFPE</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>PI_name</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>project</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>organism</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>host_organism</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="12">
+  <dataValidations count="13">
     <dataValidation sqref="H2:H1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$A$2:$A$6</formula1>
     </dataValidation>
@@ -2292,14 +2304,17 @@
     <dataValidation sqref="AK2:AK1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$I$2:$I$4</formula1>
     </dataValidation>
-    <dataValidation sqref="AQ2:AQ1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$J$2:$J$3</formula1>
+    <dataValidation sqref="AN2:AN1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Lists'!$J$2:$J$4</formula1>
     </dataValidation>
-    <dataValidation sqref="AT2:AT1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AS2:AS1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$K$2:$K$3</formula1>
     </dataValidation>
-    <dataValidation sqref="AU2:AU1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$L$2:$L$2</formula1>
+    <dataValidation sqref="AV2:AV1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Lists'!$L$2:$L$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="AW2:AW1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Lists'!$M$2:$M$2</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2312,7 +2327,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:M26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2363,15 +2378,20 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t>is_adapter_trimmed</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>FFPE</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>organism</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>host_organism</t>
         </is>
@@ -2430,10 +2450,15 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Mus musculus</t>
         </is>
@@ -2492,6 +2517,11 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t>Mus musculus</t>
         </is>
       </c>
@@ -2535,6 +2565,11 @@
       <c r="I4" t="inlineStr">
         <is>
           <t>NA</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
         </is>
       </c>
     </row>

--- a/excel_templates/wgs_wxs_panel_manifest_template.xlsx
+++ b/excel_templates/wgs_wxs_panel_manifest_template.xlsx
@@ -497,7 +497,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>PT1899</t>
+          <t>P_5P2QIUH2</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -530,7 +530,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>SM7316-11566</t>
+          <t>S_0000012</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -563,7 +563,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>AL1549608_T_WGS</t>
+          <t>AL_0000025_T_WGS</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>MODEL-PARENT-001</t>
+          <t>CNMC-XD760</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr"/>
@@ -1072,7 +1072,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>MODEL-GM-001</t>
+          <t>CNMC-XD760-mCherry-Luciferase</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr"/>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr"/>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>GCAT</t>
+          <t>AGATCGGAAGAGCGTCGTGTAGGGAAAGAGTGT</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr"/>
@@ -1883,7 +1883,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>impact trial</t>
+          <t>RBT</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">

--- a/excel_templates/wgs_wxs_panel_manifest_template.xlsx
+++ b/excel_templates/wgs_wxs_panel_manifest_template.xlsx
@@ -1974,7 +1974,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW1"/>
+  <dimension ref="A1:AX1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2026,6 +2026,7 @@
     <col width="24" customWidth="1" min="47" max="47"/>
     <col width="24" customWidth="1" min="48" max="48"/>
     <col width="24" customWidth="1" min="49" max="49"/>
+    <col width="24" customWidth="1" min="50" max="50"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2141,142 +2142,147 @@
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
+          <t>file_platform</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
           <t>sequencing_batch</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>file_name</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>file_format</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>file_size</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>file_hash_type</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>file_hash_value</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>sequencing_center</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>platform</t>
-        </is>
-      </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
+          <t>instrument_platform</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
           <t>instrument_model</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>experimental_strategy</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>target_capture_kit_name</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>target_capture_kit_link</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>bed_filename</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>is_paired_end</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>read_pair_number</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>flow_cell_barcode</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>lane_number</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>is_adapter_trimmed</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>adapter_sequencing</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>total_reads</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>mean_coverage</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>reference_genome</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>FFPE</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>PI_name</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>project</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>organism</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>host_organism</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="13">
+  <dataValidations count="12">
     <dataValidation sqref="H2:H1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$A$2:$A$6</formula1>
     </dataValidation>
@@ -2286,35 +2292,32 @@
     <dataValidation sqref="J2:J1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$C$2:$C$20</formula1>
     </dataValidation>
-    <dataValidation sqref="Y2:Y1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="Z2:Z1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$D$2:$D$26</formula1>
     </dataValidation>
-    <dataValidation sqref="AA2:AA1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AB2:AB1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$E$2:$E$6</formula1>
     </dataValidation>
-    <dataValidation sqref="AD2:AD1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$F$2:$F$9</formula1>
-    </dataValidation>
-    <dataValidation sqref="AF2:AF1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$G$2:$G$4</formula1>
-    </dataValidation>
-    <dataValidation sqref="AJ2:AJ1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$H$2:$H$3</formula1>
+    <dataValidation sqref="AG2:AG1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Lists'!$F$2:$F$4</formula1>
     </dataValidation>
     <dataValidation sqref="AK2:AK1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Lists'!$G$2:$G$3</formula1>
+    </dataValidation>
+    <dataValidation sqref="AL2:AL1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Lists'!$H$2:$H$4</formula1>
+    </dataValidation>
+    <dataValidation sqref="AO2:AO1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$I$2:$I$4</formula1>
     </dataValidation>
-    <dataValidation sqref="AN2:AN1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$J$2:$J$4</formula1>
+    <dataValidation sqref="AT2:AT1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Lists'!$J$2:$J$3</formula1>
     </dataValidation>
-    <dataValidation sqref="AS2:AS1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AW2:AW1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$K$2:$K$3</formula1>
     </dataValidation>
-    <dataValidation sqref="AV2:AV1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$L$2:$L$3</formula1>
-    </dataValidation>
-    <dataValidation sqref="AW2:AW1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$M$2:$M$2</formula1>
+    <dataValidation sqref="AX2:AX1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Lists'!$L$2:$L$2</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2327,7 +2330,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:L26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2358,40 +2361,35 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>platform</t>
+          <t>experimental_strategy</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>experimental_strategy</t>
+          <t>is_paired_end</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>is_paired_end</t>
+          <t>read_pair_number</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>read_pair_number</t>
+          <t>is_adapter_trimmed</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>is_adapter_trimmed</t>
+          <t>FFPE</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>FFPE</t>
+          <t>organism</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
-        <is>
-          <t>organism</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
         <is>
           <t>host_organism</t>
         </is>
@@ -2425,22 +2423,22 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Complete Genomics</t>
+          <t>WGS</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>WGS</t>
+          <t>True</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>True</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -2450,15 +2448,10 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>Homo sapiens</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
-        <is>
-          <t>Homo sapiens</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
         <is>
           <t>Mus musculus</t>
         </is>
@@ -2492,22 +2485,22 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Illumina</t>
+          <t>WXS</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>WXS</t>
+          <t>False</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>R2</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>False</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -2516,11 +2509,6 @@
         </is>
       </c>
       <c r="K3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
         <is>
           <t>Mus musculus</t>
         </is>
@@ -2554,20 +2542,15 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ion Torrent</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
           <t>Targeted Sequencing</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
@@ -2599,11 +2582,6 @@
           <t>SHA512</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>LS454</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2631,11 +2609,6 @@
           <t>ETag</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>SOLiD</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="B7" t="inlineStr">
@@ -2653,11 +2626,6 @@
           <t>GVCF</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>ONT</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="B8" t="inlineStr">
@@ -2675,11 +2643,6 @@
           <t>VCF</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>DNBSEQ</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="B9" t="inlineStr">
@@ -2695,11 +2658,6 @@
       <c r="D9" t="inlineStr">
         <is>
           <t>TBI</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Other</t>
         </is>
       </c>
     </row>

--- a/excel_templates/wgs_wxs_panel_manifest_template.xlsx
+++ b/excel_templates/wgs_wxs_panel_manifest_template.xlsx
@@ -2142,7 +2142,7 @@
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>file_platform</t>
+          <t>file_source_platform</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">

--- a/excel_templates/wgs_wxs_panel_manifest_template.xlsx
+++ b/excel_templates/wgs_wxs_panel_manifest_template.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Lists" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Data Dictionary'!$A$1:$G$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Data Dictionary'!$A$1:$G$51</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1085,12 +1085,12 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>SMB directory path on the L Drive for the source data</t>
+          <t>SMB directory path on the L Drive for the source data. Required when file_source_platform is local_drive or bti_aws_and_local_drive</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr"/>
@@ -1114,12 +1114,12 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>S3 URI for the submitted data location</t>
+          <t>S3 URI for the submitted data location. Required when file_source_platform is bti_aws or bti_aws_and_local_drive</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr"/>
@@ -1138,20 +1138,24 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>sequencing_batch</t>
+          <t>file_source_platform</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Sequencing batch identifier</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr"/>
+          <t>Source platform where files are stored and from which they are harmonized</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>"bti_aws", "local_drive", "bti_aws_and_local_drive", "cgc", "kids_first", "sra", "synapse"</t>
+        </is>
+      </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -1159,7 +1163,7 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>30-XXXXXXXX</t>
+          <t>bti_aws</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr"/>
@@ -1167,17 +1171,17 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>file_name</t>
+          <t>sequencing_batch</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Name of the file</t>
+          <t>Sequencing batch identifier</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr"/>
@@ -1188,7 +1192,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>NCI-11Plex-13-F12A-z11358.fastq</t>
+          <t>30-XXXXXXXX</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr"/>
@@ -1196,7 +1200,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>file_format</t>
+          <t>file_name</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1206,14 +1210,10 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Format of the file</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>"FASTQ", "BAM", "BAI", "CRAM", "CRAI", "GVCF", "VCF", "TBI", "MAF", "PDF", "HTML", "DCM", "IDAT", "SVS", "GPR", "CNS", "TXT", "PNG", "CSV", "PED", "SEG", "TAR", "TSV", "mzML", "raw"</t>
-        </is>
-      </c>
+          <t>Name of the file</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr"/>
       <c r="E26" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -1221,7 +1221,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>FASTQ</t>
+          <t>NCI-11Plex-13-F12A-z11358.fastq</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr"/>
@@ -1229,7 +1229,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>file_size</t>
+          <t>file_format</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1239,18 +1239,22 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Reported file size in bytes</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr"/>
+          <t>Format of the file</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>"FASTQ", "BAM", "BAI", "CRAM", "CRAI", "GVCF", "VCF", "TBI", "MAF", "PDF", "HTML", "DCM", "IDAT", "SVS", "GPR", "CNS", "TXT", "PNG", "CSV", "PED", "SEG", "TAR", "TSV", "mzML", "raw"</t>
+        </is>
+      </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>529600</t>
+          <t>FASTQ</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr"/>
@@ -1258,7 +1262,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>file_hash_type</t>
+          <t>file_size</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1268,22 +1272,18 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Hash algorithm used to generate file hash</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>"MD5", "SHA1", "SHA256", "SHA512", "ETag"</t>
-        </is>
-      </c>
+          <t>Reported file size in bytes</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr"/>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>MD5</t>
+          <t>529600</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr"/>
@@ -1291,7 +1291,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>file_hash_value</t>
+          <t>file_hash_type</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1301,10 +1301,14 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Full has value of the file</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr"/>
+          <t>Hash algorithm used to generate file hash</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>"MD5", "SHA1", "SHA256", "SHA512", "ETag"</t>
+        </is>
+      </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -1312,7 +1316,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>938c2cc0dcc05f2b68c4287040cfcf71</t>
+          <t>MD5</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr"/>
@@ -1320,17 +1324,17 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>sequencing_center</t>
+          <t>file_hash_value</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Name of the center generating sequencing data</t>
+          <t>Full has value of the file</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr"/>
@@ -1341,7 +1345,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Harvard Med School</t>
+          <t>938c2cc0dcc05f2b68c4287040cfcf71</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr"/>
@@ -1349,24 +1353,20 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>platform</t>
+          <t>sequencing_center</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Name of the platform used to obtain data</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>"Complete Genomics", "Illumina", "Ion Torrent", "LS454", "SOLiD", "ONT", "DNBSEQ", "Other"</t>
-        </is>
-      </c>
+          <t>Name of the center generating sequencing data</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr"/>
       <c r="E31" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Illumina</t>
+          <t>Harvard Med School</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr"/>
@@ -1382,32 +1382,32 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>instrument_model</t>
+          <t>instrument_platform</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Specific model of sequencing instrument used.</t>
+          <t>Name of the platform used to obtain data</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>"Complete Genomics", "Illumina", "Ion Torrent", "LS454", "SOLiD", "ONT", "DNBSEQ", "Other"</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Model name of the instrument used for sequencing</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>NovaSeq 6000</t>
+          <t>Illumina</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr"/>
@@ -1415,32 +1415,32 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>experimental_strategy</t>
+          <t>instrument_model</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>The sequencing strategy used to generate the data file.</t>
+          <t>Specific model of sequencing instrument used.</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>"WGS", "WXS", "Targeted Sequencing"</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>Model name of the instrument used for sequencing</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>WGS</t>
+          <t>NovaSeq 6000</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr"/>
@@ -1448,32 +1448,40 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>target_capture_kit_name</t>
+          <t>experimental_strategy</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Description that can uniquely identify a target capture kit. Required for WXS and Targeted Sequencing.</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr"/>
+          <t>The sequencing strategy used to generate the data file.</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>"WGS", "WXS", "Targeted Sequencing"</t>
+        </is>
+      </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr"/>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>WGS</t>
+        </is>
+      </c>
       <c r="G34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>target_capture_kit_link</t>
+          <t>target_capture_kit_name</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -1483,7 +1491,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Full download link for the bed file corresponding to the target panel or capture kit used for sequence enrichment.</t>
+          <t>Description that can uniquely identify a target capture kit. Required for WXS and Targeted Sequencing.</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr"/>
@@ -1498,7 +1506,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>bed_filename</t>
+          <t>target_capture_kit_link</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -1508,7 +1516,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Name of the capture kit bed file. Required for WXS and Targeted Sequencing.</t>
+          <t>Full download link for the bed file corresponding to the target panel or capture kit used for sequence enrichment.</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr"/>
@@ -1523,65 +1531,57 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>is_paired_end</t>
+          <t>bed_filename</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>If fastq/bam files, are the reads paired end?</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>"True", "False"</t>
-        </is>
-      </c>
+          <t>Name of the capture kit bed file. Required for WXS and Targeted Sequencing.</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr"/>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr"/>
       <c r="G37" s="2" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>read_pair_number</t>
+          <t>is_paired_end</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Denotes whether a submitted FASTQ file contains forward (R1) or reverse (R2) reads for paired-end sequencing. Required when inputs are FASTQ files.</t>
+          <t>If fastq/bam files, are the reads paired end?</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>"R1", "R2", "NA"</t>
+          <t>"True", "False"</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>R1</t>
+          <t>True</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr"/>
@@ -1589,7 +1589,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>flow_cell_barcode</t>
+          <t>read_pair_number</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -1599,10 +1599,14 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Flow cell barcode. Wrong or missing information may affect analysis results. Required when inputs are FASTQ files.</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr"/>
+          <t>Denotes whether a submitted FASTQ file contains forward (R1) or reverse (R2) reads for paired-end sequencing. Required when inputs are FASTQ files.</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>"R1", "R2", "NA"</t>
+        </is>
+      </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -1610,7 +1614,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>H0164ALXX140820</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr"/>
@@ -1618,7 +1622,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>lane_number</t>
+          <t>flow_cell_barcode</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -1628,7 +1632,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>The basic machine unit for sequencing. For Illumina machines, this reflects the physical lane number. Wrong or missing information may affect analysis results. Required when inputs are FASTQ files.</t>
+          <t>Flow cell barcode. Wrong or missing information may affect analysis results. Required when inputs are FASTQ files.</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr"/>
@@ -1639,7 +1643,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>H0164ALXX140820</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr"/>
@@ -1647,7 +1651,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>is_adapter_trimmed</t>
+          <t>lane_number</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -1657,22 +1661,18 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Were adapters trimmed from sequencing data? Not required, as adapter presence is detected downstream; fill in if known. Only applies to FASTQ files.</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>"True", "False", "Unknown"</t>
-        </is>
-      </c>
+          <t>The basic machine unit for sequencing. For Illumina machines, this reflects the physical lane number. Wrong or missing information may affect analysis results. Required when inputs are FASTQ files.</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr"/>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>boolean/string</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr"/>
@@ -1680,7 +1680,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>adapter_sequencing</t>
+          <t>is_adapter_trimmed</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -1690,18 +1690,22 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Base sequence of the sequencing adapter. Only applies when adapters were not trimmed.</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr"/>
+          <t>Were adapters trimmed from sequencing data? Not required, as adapter presence is detected downstream; fill in if known. Only applies to FASTQ files.</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>"True", "False", "Unknown"</t>
+        </is>
+      </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean/string</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>AGATCGGAAGAGCGTCGTGTAGGGAAAGAGTGT</t>
+          <t>False</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr"/>
@@ -1709,7 +1713,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>total_reads</t>
+          <t>adapter_sequencing</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -1719,18 +1723,18 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Total number of reads that align to the reference.</t>
+          <t>Base sequence of the sequencing adapter. Only applies when adapters were not trimmed.</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr"/>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>525600</t>
+          <t>AGATCGGAAGAGCGTCGTGTAGGGAAAGAGTGT</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr"/>
@@ -1738,7 +1742,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>mean_coverage</t>
+          <t>total_reads</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -1748,7 +1752,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Mean coverage for whole genome sequencing, or mean target coverage for whole exome and targeted sequencing, collected from Picard Tools.</t>
+          <t>Total number of reads that align to the reference.</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr"/>
@@ -1759,7 +1763,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>525600</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr"/>
@@ -1767,28 +1771,28 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>reference_genome</t>
+          <t>mean_coverage</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Reference genome version.</t>
+          <t>Mean coverage for whole genome sequencing, or mean target coverage for whole exome and targeted sequencing, collected from Picard Tools.</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr"/>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>GRCH38</t>
+          <t>60</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr"/>
@@ -1796,7 +1800,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>FFPE</t>
+          <t>reference_genome</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -1806,22 +1810,18 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Is the sample preserved in FFPE</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>"True", "False"</t>
-        </is>
-      </c>
+          <t>Reference genome version.</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr"/>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>string</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>GRCH38</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr"/>
@@ -1829,7 +1829,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>PI_name</t>
+          <t>FFPE</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -1839,30 +1839,30 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Principal Investigator of the project</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr"/>
+          <t>Is the sample preserved in FFPE</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>"True", "False"</t>
+        </is>
+      </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>boolean</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>Fonseca</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>project</t>
+          <t>PI_name</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -1872,7 +1872,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Short name of the project</t>
+          <t>Principal Investigator of the project</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr"/>
@@ -1883,7 +1883,7 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>RBT</t>
+          <t>Fonseca</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -1895,7 +1895,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>organism</t>
+          <t>project</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -1905,14 +1905,10 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Binomial name of organism with full genus name</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>"Homo sapiens", "Mus musculus"</t>
-        </is>
-      </c>
+          <t>Short name of the project</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr"/>
       <c r="E49" s="2" t="inlineStr">
         <is>
           <t>string</t>
@@ -1920,50 +1916,87 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>Homo sapiens</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="inlineStr"/>
+          <t>RBT</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>organism</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Binomial name of organism with full genus name</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>"Homo sapiens", "Mus musculus"</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>Homo sapiens</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
           <t>host_organism</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
         <is>
           <t>Host organism binomial name when the sequenced sample is a xenograft. Required when compisition is "Patient Derived Xenograft" or "Xenograft"</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>"Mus musculus"</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>Mus musculus</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G50"/>
+  <autoFilter ref="A1:G51"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2282,7 +2315,7 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations count="12">
+  <dataValidations count="14">
     <dataValidation sqref="H2:H1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$A$2:$A$6</formula1>
     </dataValidation>
@@ -2292,32 +2325,38 @@
     <dataValidation sqref="J2:J1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$C$2:$C$20</formula1>
     </dataValidation>
+    <dataValidation sqref="W2:W1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Lists'!$D$2:$D$8</formula1>
+    </dataValidation>
     <dataValidation sqref="Z2:Z1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$D$2:$D$26</formula1>
+      <formula1>'Lists'!$E$2:$E$26</formula1>
     </dataValidation>
     <dataValidation sqref="AB2:AB1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$E$2:$E$6</formula1>
+      <formula1>'Lists'!$F$2:$F$6</formula1>
+    </dataValidation>
+    <dataValidation sqref="AE2:AE1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Lists'!$G$2:$G$9</formula1>
     </dataValidation>
     <dataValidation sqref="AG2:AG1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$F$2:$F$4</formula1>
+      <formula1>'Lists'!$H$2:$H$4</formula1>
     </dataValidation>
     <dataValidation sqref="AK2:AK1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$G$2:$G$3</formula1>
+      <formula1>'Lists'!$I$2:$I$3</formula1>
     </dataValidation>
     <dataValidation sqref="AL2:AL1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$H$2:$H$4</formula1>
+      <formula1>'Lists'!$J$2:$J$4</formula1>
     </dataValidation>
     <dataValidation sqref="AO2:AO1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$I$2:$I$4</formula1>
+      <formula1>'Lists'!$K$2:$K$4</formula1>
     </dataValidation>
     <dataValidation sqref="AT2:AT1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$J$2:$J$3</formula1>
+      <formula1>'Lists'!$L$2:$L$3</formula1>
     </dataValidation>
     <dataValidation sqref="AW2:AW1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$K$2:$K$3</formula1>
+      <formula1>'Lists'!$M$2:$M$3</formula1>
     </dataValidation>
     <dataValidation sqref="AX2:AX1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>'Lists'!$L$2:$L$2</formula1>
+      <formula1>'Lists'!$N$2:$N$2</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2330,7 +2369,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:N26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2351,45 +2390,55 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>file_source_platform</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>file_format</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>file_hash_type</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>instrument_platform</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
         <is>
           <t>experimental_strategy</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>is_paired_end</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>read_pair_number</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>is_adapter_trimmed</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>FFPE</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>organism</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>host_organism</t>
         </is>
@@ -2413,45 +2462,55 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>bti_aws</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>FASTQ</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>MD5</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Complete Genomics</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
         <is>
           <t>WGS</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Homo sapiens</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Mus musculus</t>
         </is>
@@ -2475,40 +2534,50 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>local_drive</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>BAM</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>SHA1</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Illumina</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
         <is>
           <t>WXS</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
         <is>
           <t>Mus musculus</t>
         </is>
@@ -2532,25 +2601,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>bti_aws_and_local_drive</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>BAI</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>SHA256</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Ion Torrent</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
         <is>
           <t>Targeted Sequencing</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>Unknown</t>
         </is>
@@ -2574,12 +2653,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>cgc</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>CRAM</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>SHA512</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>LS454</t>
         </is>
       </c>
     </row>
@@ -2601,12 +2690,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>kids_first</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>CRAI</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>ETag</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>SOLiD</t>
         </is>
       </c>
     </row>
@@ -2623,7 +2722,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>sra</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>GVCF</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>ONT</t>
         </is>
       </c>
     </row>
@@ -2640,7 +2749,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>synapse</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>VCF</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>DNBSEQ</t>
         </is>
       </c>
     </row>
@@ -2655,9 +2774,14 @@
           <t>Patient Derived Organoid</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>TBI</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -2672,7 +2796,7 @@
           <t>Peripheral Blood Mononuclear Cells</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>MAF</t>
         </is>
@@ -2689,7 +2813,7 @@
           <t>Peripheral Whole Blood</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
@@ -2706,7 +2830,7 @@
           <t>Saliva</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>HTML</t>
         </is>
@@ -2723,7 +2847,7 @@
           <t>Solid Tissue</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>DCM</t>
         </is>
@@ -2740,7 +2864,7 @@
           <t>Umbilical Cord Blood</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>IDAT</t>
         </is>
@@ -2752,7 +2876,7 @@
           <t>Patient-Derived T Cells</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>SVS</t>
         </is>
@@ -2764,7 +2888,7 @@
           <t>Modified T Cells</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>GPR</t>
         </is>
@@ -2776,7 +2900,7 @@
           <t>Patient-Derived Primary Cells</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>CNS</t>
         </is>
@@ -2788,7 +2912,7 @@
           <t>iPSC-Derived Organoid</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>TXT</t>
         </is>
@@ -2800,7 +2924,7 @@
           <t>Cerebrospinal Fluid</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>PNG</t>
         </is>
@@ -2812,49 +2936,49 @@
           <t>Embryonic Stem Cell Derived Cell Line</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>CSV</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="D21" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>PED</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="D22" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>SEG</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="D23" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>TAR</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="D24" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>TSV</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="D25" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>mzML</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="D26" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>raw</t>
         </is>

--- a/excel_templates/wgs_wxs_panel_manifest_template.xlsx
+++ b/excel_templates/wgs_wxs_panel_manifest_template.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Lists" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Data Dictionary'!$A$1:$G$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Data Dictionary'!$A$1:$G$52</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:G52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1995,8 +1995,41 @@
         </is>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>reported_gender</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Reported gender of the participant. Required when organism is "Homo sapiens"</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>"Female", "Male", "Not Reported"</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G51"/>
+  <autoFilter ref="A1:G52"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2007,7 +2040,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX1"/>
+  <dimension ref="A1:AY1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2060,6 +2093,7 @@
     <col width="24" customWidth="1" min="48" max="48"/>
     <col width="24" customWidth="1" min="49" max="49"/>
     <col width="24" customWidth="1" min="50" max="50"/>
+    <col width="24" customWidth="1" min="51" max="51"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2313,9 +2347,14 @@
           <t>host_organism</t>
         </is>
       </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>reported_gender</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <dataValidations count="14">
+  <dataValidations count="15">
     <dataValidation sqref="H2:H1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$A$2:$A$6</formula1>
     </dataValidation>
@@ -2358,6 +2397,9 @@
     <dataValidation sqref="AX2:AX1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lists'!$N$2:$N$2</formula1>
     </dataValidation>
+    <dataValidation sqref="AY2:AY1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>'Lists'!$O$2:$O$4</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2369,7 +2411,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N26"/>
+  <dimension ref="A1:O26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2443,6 +2485,11 @@
           <t>host_organism</t>
         </is>
       </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>reported_gender</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2515,6 +2562,11 @@
           <t>Mus musculus</t>
         </is>
       </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2582,6 +2634,11 @@
           <t>Mus musculus</t>
         </is>
       </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2632,6 +2689,11 @@
       <c r="K4" t="inlineStr">
         <is>
           <t>Unknown</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Not Reported</t>
         </is>
       </c>
     </row>

--- a/excel_templates/wgs_wxs_panel_manifest_template.xlsx
+++ b/excel_templates/wgs_wxs_panel_manifest_template.xlsx
@@ -1805,12 +1805,12 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Reference genome version.</t>
+          <t>Reference genome version. Required when file_format is "BAM" or "CRAM"</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr"/>
